--- a/docs/architecture/SSE_Quadro_Comparativo_FAM.xlsx
+++ b/docs/architecture/SSE_Quadro_Comparativo_FAM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="137">
   <si>
     <t xml:space="preserve">Storm Shield Enterprise — Quadro Comparativo: Leading Practices (Oracle/NetSuite FAM) vs SSE</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">Observações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase do Roadmap</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURAÇÃO E DADOS MESTRE</t>
@@ -64,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">SSE simplifica: ativo não passa por inventory. Registro direto via financial_transaction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 3 — Contab. + FAM</t>
   </si>
   <si>
     <t xml:space="preserve">Plano de contas — 4 contas obrigatórias por categoria:
@@ -172,6 +178,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pode ser implementado via workflow: criar N ativos filhos e desativar o pai. Considerar para v2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backlog (v2)</t>
   </si>
   <si>
     <t xml:space="preserve">Transferência de ativo (entre categorias, localizações, departamentos)</t>
@@ -261,6 +270,9 @@
     <t xml:space="preserve">Multi-book accounting (contábil + fiscal) pode ser adicionado em v2 se necessário.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fase 4 — Compliance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Catch-up de períodos anteriores não processados</t>
   </si>
   <si>
@@ -449,6 +461,21 @@
   </si>
   <si>
     <t xml:space="preserve">% Cobertura Total + Parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTRIBUIÇÃO POR FASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core FAM: configuração, aquisição, depreciação, descarte e relatórios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 4 — Compliance Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-book accounting (depreciação alternativa fiscal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de ativos + Lease Accounting (IFRS 16 / ASC 842)</t>
   </si>
 </sst>
 </file>
@@ -527,7 +554,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,12 +581,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8DAEF"/>
+        <bgColor rgb="FFD5D8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEF9E7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFADBD8"/>
+        <bgColor rgb="FFE8DAEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEBD0"/>
+        <bgColor rgb="FFFADBD8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -573,6 +618,36 @@
       </left>
       <right style="thin">
         <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D8DC"/>
       </right>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
@@ -621,11 +696,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -638,7 +717,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -654,11 +737,23 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -666,8 +761,36 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -704,7 +827,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD5D8DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -714,13 +837,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8DAEF"/>
       <rgbColor rgb="FFD5F5E3"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFDEBD0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFADBD8"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -922,741 +1045,894 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="B14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="B17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="B18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="B20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="B24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="B26" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="B27" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="B28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="B30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="B32" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="B33" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="B34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="B35" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="B36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="n">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11" t="s">
+      <c r="C37" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11" t="s">
+      <c r="F37" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="G37" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="8" t="n">
         <f aca="false">COUNTIF(D5:D100,"*Coberto*")</f>
         <v>23</v>
       </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="6" t="n">
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="8" t="n">
         <f aca="false">COUNTIF(D5:D100,"*Parcial*")</f>
         <v>3</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" s="6" t="n">
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="8" t="n">
         <f aca="false">COUNTIF(D5:D100,"*N/A*")</f>
         <v>0</v>
       </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="6" t="str">
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="8" t="str">
         <f aca="false">ROUND((C42+C43)/C41*100,1)&amp;"%"</f>
         <v>100%</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="20" t="n">
+        <f aca="false">COUNTIF(G6:G37,"*Fase 3*")</f>
+        <v>23</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="20" t="n">
+        <f aca="false">COUNTIF(G6:G37,"*Fase 4*")</f>
+        <v>1</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="20" t="n">
+        <f aca="false">COUNTIF(G6:G37,"*Backlog*")</f>
+        <v>2</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A39:F39"/>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D50:G50"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
